--- a/artfynd/A 39933-2023 artfynd.xlsx
+++ b/artfynd/A 39933-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39933-2023 artfynd.xlsx
+++ b/artfynd/A 39933-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>100131715</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659026.1649080083</v>
+        <v>659027</v>
       </c>
       <c r="R2" t="n">
-        <v>6643275.807296977</v>
+        <v>6643276</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -802,12 +797,7 @@
         <v>110068474</v>
       </c>
       <c r="B3" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659026.1649080083</v>
+        <v>659027</v>
       </c>
       <c r="R3" t="n">
-        <v>6643275.807296977</v>
+        <v>6643276</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
